--- a/tabular/genus/copi-refseqs-side-data.xlsx
+++ b/tabular/genus/copi-refseqs-side-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10308"/>
   <workbookPr date1904="1" showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/robertgifford/Projects/virus/comparative/DNAss/Parvoviridae-GLUE/tabular/genus/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/diversity/Parvovirus-GLUE/tabular/genus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65A355AB-B710-C145-9833-9DF9698E3081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EF79655-8E42-CF40-B531-D62F848D85B1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14020" yWindow="8500" windowWidth="28800" windowHeight="17540" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="880" yWindow="500" windowWidth="27920" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REFSET" sheetId="3" r:id="rId1"/>
@@ -2073,7 +2073,32 @@
     <cellStyle name="Hyperlink" xfId="913" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF660066"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <colors>
     <mruColors>
@@ -2091,6 +2116,28 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DFA6D4CC-C4DF-9C4C-B16A-2650649ED9D5}" name="Table1" displayName="Table1" ref="A1:M9" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:M9" xr:uid="{2BA39DBC-9465-EA4A-8106-7AA020CDB3DD}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{06A23723-9148-FD4C-9AB6-01ADCEA4ED9D}" name="sequenceID"/>
+    <tableColumn id="2" xr3:uid="{B16089D4-3A7C-0A43-ADCF-6D74FE92B597}" name="virus_name"/>
+    <tableColumn id="3" xr3:uid="{3ACF7E13-97E6-E245-9D62-C7630A04FF3D}" name="virus_full_name"/>
+    <tableColumn id="4" xr3:uid="{E870E1FD-8944-3F43-B5BA-11DCD289F1B0}" name="host_species"/>
+    <tableColumn id="5" xr3:uid="{D8128C94-5806-CA44-B77C-96B8BE3A06D0}" name="assign_clade"/>
+    <tableColumn id="6" xr3:uid="{62A9A961-28E9-CD44-87B3-1515710C1937}" name="virus_subfamily"/>
+    <tableColumn id="7" xr3:uid="{8200D97F-8729-CD4F-B05B-A8747CC3C7FC}" name="virus_genus"/>
+    <tableColumn id="8" xr3:uid="{B1928E00-0C34-514E-918E-359C70B3301D}" name="assign_subclade"/>
+    <tableColumn id="9" xr3:uid="{4CD93B90-2200-DB4F-B120-658AE06A9FA3}" name="virus_clade_ns"/>
+    <tableColumn id="10" xr3:uid="{9E1E8F93-6361-3540-A4DC-371F6D1506C2}" name="virus_subclade_ns"/>
+    <tableColumn id="11" xr3:uid="{0F1F63A4-FBC3-D448-8F3C-707FC936144C}" name="virus_clade_vp"/>
+    <tableColumn id="12" xr3:uid="{8AF06CA0-4049-4345-BF8A-E1C15E6210F9}" name="virus_subclade_vp"/>
+    <tableColumn id="13" xr3:uid="{88A30CCF-77F7-CE41-9760-60FCB60BAC8B}" name="lab_construct"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2422,11 +2469,12 @@
     <col min="2" max="2" width="17.33203125" customWidth="1"/>
     <col min="3" max="3" width="41" customWidth="1"/>
     <col min="4" max="4" width="26.33203125" customWidth="1"/>
-    <col min="5" max="6" width="15.1640625" customWidth="1"/>
+    <col min="5" max="5" width="15.1640625" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" customWidth="1"/>
     <col min="7" max="8" width="18.6640625" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
     <col min="10" max="10" width="18.5" customWidth="1"/>
-    <col min="11" max="11" width="15.5" customWidth="1"/>
+    <col min="11" max="11" width="15.83203125" customWidth="1"/>
     <col min="12" max="12" width="19.5" customWidth="1"/>
     <col min="13" max="13" width="15.33203125" customWidth="1"/>
   </cols>
@@ -2806,6 +2854,9 @@
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
       <mx:PLV Mode="0" OnePage="0" WScale="0"/>
